--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260619_210015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260619_210015.xlsx
@@ -6348,7 +6348,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260619_210015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260619_210015.xlsx
@@ -6348,7 +6348,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
